--- a/02-Referencias/ATUA/Março/ATUA_despesas_fechamento_03-2026.xlsx
+++ b/02-Referencias/ATUA/Março/ATUA_despesas_fechamento_03-2026.xlsx
@@ -16,7 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="#.##0,00"/>
+    <numFmt numFmtId="167" formatCode="DD/MM/YYYY"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -49,9 +54,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -686,30 +693,22 @@
           <t>ALUGUEL03/2026-GSL</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.003,50</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.003,50</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1.003,50</t>
-        </is>
+      <c r="T2" s="2" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>-1003.5</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>-1003.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="X2" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
@@ -832,30 +831,22 @@
           <t>664</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.671,35</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.671,35</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1.671,35</t>
-        </is>
+      <c r="T3" s="2" t="n">
+        <v>1671.35</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>-1671.35</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-1671.35</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="X3" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
@@ -978,30 +969,22 @@
           <t>1418944</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>140,13</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>140,13</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>140,13</t>
-        </is>
+      <c r="T4" s="2" t="n">
+        <v>140.13</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>-140.13</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-140.13</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="X4" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
@@ -1124,30 +1107,22 @@
           <t>1419646</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>252,25</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>252,25</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>252,25</t>
-        </is>
+      <c r="T5" s="2" t="n">
+        <v>252.25</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>-252.25</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-252.25</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="X5" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
@@ -1270,30 +1245,22 @@
           <t>1420383</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>105,69</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>105,69</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>105,69</t>
-        </is>
+      <c r="T6" s="2" t="n">
+        <v>105.69</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>-105.69</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-105.69</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="X6" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -1416,30 +1383,22 @@
           <t>1420420</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>126,48</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>126,48</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>126,48</t>
-        </is>
+      <c r="T7" s="2" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>-126.48</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-126.48</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="X7" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
@@ -1539,17 +1498,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>6.6.1</t>
+          <t>7.5.17</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>FRETE DE TERCEIROS</t>
+          <t>TAXAS</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>6.6.1 FRETE DE TERCEIROS</t>
+          <t>7.5.17 TAXAS</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1562,30 +1521,22 @@
           <t>1421695</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>199,00</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>199,00</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>199,00</t>
-        </is>
+      <c r="T8" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>-199</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-199</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="X8" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
@@ -1708,30 +1659,22 @@
           <t>0010584</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>36,00</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>36,00</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>36,00</t>
-        </is>
+      <c r="T9" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>-36</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-36</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
+      <c r="X9" s="3" t="n">
+        <v>46085</v>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
@@ -1854,30 +1797,22 @@
           <t>0010736</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>87,00</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>87,00</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>87,00</t>
-        </is>
+      <c r="T10" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>-87</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-87</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
+      <c r="X10" s="3" t="n">
+        <v>46085</v>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
@@ -2000,30 +1935,22 @@
           <t>17377</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.360,00</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.360,00</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.360,00</t>
-        </is>
+      <c r="T11" s="2" t="n">
+        <v>1360</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>-1360</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>-1360</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
+      <c r="X11" s="3" t="n">
+        <v>46085</v>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
@@ -2146,30 +2073,22 @@
           <t>PROLAB022026</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.442,69</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.442,69</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1.442,69</t>
-        </is>
+      <c r="T12" s="2" t="n">
+        <v>1442.69</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>-1442.69</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>-1442.69</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
+      <c r="X12" s="3" t="n">
+        <v>46086</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
@@ -2292,30 +2211,22 @@
           <t>440846</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>3.507,40</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>3.507,40</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>3.507,40</t>
-        </is>
+      <c r="T13" s="2" t="n">
+        <v>3507.4</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>-3507.4</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>-3507.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+      <c r="X13" s="3" t="n">
+        <v>46087</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
@@ -2438,30 +2349,22 @@
           <t>239</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>4.093,91</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>4.093,91</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>4.093,91</t>
-        </is>
+      <c r="T14" s="2" t="n">
+        <v>4093.91</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>-4093.91</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>-4093.91</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Transporte</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+      <c r="X14" s="3" t="n">
+        <v>46087</v>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
@@ -2584,30 +2487,22 @@
           <t>240</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>4.349,86</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>4.349,86</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>4.349,86</t>
-        </is>
+      <c r="T15" s="2" t="n">
+        <v>4349.86</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>-4349.86</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>-4349.86</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Transporte</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+      <c r="X15" s="3" t="n">
+        <v>46087</v>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
@@ -2730,30 +2625,22 @@
           <t>241</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>4.060,96</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>4.060,96</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>4.060,96</t>
-        </is>
+      <c r="T16" s="2" t="n">
+        <v>4060.96</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>-4060.96</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>-4060.96</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Transporte</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+      <c r="X16" s="3" t="n">
+        <v>46087</v>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
@@ -2876,30 +2763,22 @@
           <t>ICMS022026GSL02</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>32.326,44</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>32.326,44</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>32.326,44</t>
-        </is>
+      <c r="T17" s="2" t="n">
+        <v>32326.44</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>-32326.44</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>-32326.44</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+      <c r="X17" s="3" t="n">
+        <v>46087</v>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
@@ -3022,30 +2901,22 @@
           <t>ICMS022026GSL03</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>8.294,87</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>8.294,87</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>8.294,87</t>
-        </is>
+      <c r="T18" s="2" t="n">
+        <v>8294.870000000001</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>-8294.870000000001</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>-8294.870000000001</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+      <c r="X18" s="3" t="n">
+        <v>46087</v>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
@@ -3168,30 +3039,22 @@
           <t>478301</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>360,04</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>360,04</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>360,04</t>
-        </is>
+      <c r="T19" s="2" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>-360.04</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>-360.04</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
+      <c r="X19" s="3" t="n">
+        <v>46090</v>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
@@ -3314,30 +3177,22 @@
           <t>452978</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2.045,79</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>2.045,79</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2.045,79</t>
-        </is>
+      <c r="T20" s="2" t="n">
+        <v>2045.79</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>-2045.79</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>-2045.79</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
+      <c r="X20" s="3" t="n">
+        <v>46090</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
@@ -3460,30 +3315,22 @@
           <t>ICMS022026GSL01</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>31.602,14</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>31.602,14</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>31.602,14</t>
-        </is>
+      <c r="T21" s="2" t="n">
+        <v>31602.14</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>-31602.14</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>-31602.14</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X21" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
@@ -3606,30 +3453,22 @@
           <t>TRPED140226</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
+      <c r="T22" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>-3.37</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X22" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
@@ -3752,30 +3591,22 @@
           <t>TRPED180226</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>29,76</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>29,76</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>29,76</t>
-        </is>
+      <c r="T23" s="2" t="n">
+        <v>29.76</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>-29.76</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>-29.76</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X23" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
@@ -3898,30 +3729,22 @@
           <t>TRPED190226</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>9,49</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>9,49</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>9,49</t>
-        </is>
+      <c r="T24" s="2" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>-9.49</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>-9.49</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X24" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
@@ -4044,30 +3867,22 @@
           <t>TRPED200226</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
+      <c r="T25" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>-27</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>-27</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X25" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
@@ -4190,30 +4005,22 @@
           <t>TRPED230226</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>29,34</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>29,34</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>29,34</t>
-        </is>
+      <c r="T26" s="2" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>-29.34</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>-29.34</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X26" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
@@ -4336,30 +4143,22 @@
           <t>TRPED240226</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>54,05</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>54,05</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>54,05</t>
-        </is>
+      <c r="T27" s="2" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>-54.05</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>-54.05</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X27" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
@@ -4482,30 +4281,22 @@
           <t>TRPED250226</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>17,63</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>17,63</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>17,63</t>
-        </is>
+      <c r="T28" s="2" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>-17.63</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>-17.63</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X28" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
@@ -4628,30 +4419,22 @@
           <t>TRPED260226</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>26,08</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>26,08</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>26,08</t>
-        </is>
+      <c r="T29" s="2" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>-26.08</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>-26.08</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X29" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
@@ -4774,30 +4557,22 @@
           <t>TRPED270226</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>21,55</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>21,55</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>21,55</t>
-        </is>
+      <c r="T30" s="2" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>-21.55</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>-21.55</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X30" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
@@ -4920,30 +4695,22 @@
           <t>TFCM040226</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>11,87</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>11,87</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>11,87</t>
-        </is>
+      <c r="T31" s="2" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>-11.87</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>-11.87</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
+      <c r="X31" s="3" t="n">
+        <v>46091</v>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
@@ -5066,30 +4833,22 @@
           <t>1422846</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>62,12</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>62,12</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>62,12</t>
-        </is>
+      <c r="T32" s="2" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>-62.12</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>-62.12</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
+      <c r="X32" s="3" t="n">
+        <v>46092</v>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
@@ -5212,30 +4971,22 @@
           <t>TR130326</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>115,60</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>115,60</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>115,60</t>
-        </is>
+      <c r="T33" s="2" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>-115.6</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>-115.6</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
+      <c r="X33" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
@@ -5358,30 +5109,22 @@
           <t>TRPED020326</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
+      <c r="T34" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>-13.68</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>-13.68</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
+      <c r="X34" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
@@ -5504,30 +5247,22 @@
           <t>TRPED030326</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>39,25</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>39,25</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>39,25</t>
-        </is>
+      <c r="T35" s="2" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>-39.25</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>-39.25</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
+      <c r="X35" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
@@ -5650,30 +5385,22 @@
           <t>TRPED040326</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>18,46</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>18,46</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>18,46</t>
-        </is>
+      <c r="T36" s="2" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>-18.46</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>-18.46</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
+      <c r="X36" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
@@ -5796,30 +5523,22 @@
           <t>TRPED050326</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>31,07</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>31,07</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>31,07</t>
-        </is>
+      <c r="T37" s="2" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>-31.07</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>-31.07</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
+      <c r="X37" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
@@ -5942,30 +5661,22 @@
           <t>TRPED060326</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>20,13</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>20,13</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>20,13</t>
-        </is>
+      <c r="T38" s="2" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>-20.13</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>-20.13</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
+      <c r="X38" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
@@ -6088,30 +5799,22 @@
           <t>1421203</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>84,03</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>84,03</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>84,03</t>
-        </is>
+      <c r="T39" s="2" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>-84.03</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>-84.03</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
+      <c r="X39" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
@@ -6234,30 +5937,22 @@
           <t>ARRECADAÇÃO022026</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>7.198,98</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>7.198,98</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>7.198,98</t>
-        </is>
+      <c r="T40" s="2" t="n">
+        <v>7198.98</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>-7198.98</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>-7198.98</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>19/03/2026</t>
-        </is>
+      <c r="X40" s="3" t="n">
+        <v>46100</v>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
@@ -6380,30 +6075,22 @@
           <t>TRPED090326</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>26,57</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>26,57</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>26,57</t>
-        </is>
+      <c r="T41" s="2" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>-26.57</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>-26.57</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X41" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
@@ -6526,30 +6213,22 @@
           <t>TRPED100326</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>52,21</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>52,21</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>52,21</t>
-        </is>
+      <c r="T42" s="2" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>-52.21</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>-52.21</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X42" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
@@ -6672,30 +6351,22 @@
           <t>TRPED110326</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>75,70</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>75,70</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>75,70</t>
-        </is>
+      <c r="T43" s="2" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>-75.7</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>-75.7</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X43" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
@@ -6818,30 +6489,22 @@
           <t>TRPED120326</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
+      <c r="T44" s="2" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>-19.56</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>-19.56</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X44" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
@@ -6964,30 +6627,22 @@
           <t>TRPED130326</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>25,88</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>25,88</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>25,88</t>
-        </is>
+      <c r="T45" s="2" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>-25.88</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>-25.88</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X45" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
@@ -7110,30 +6765,22 @@
           <t>TFCM100326</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
+      <c r="T46" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>-2.83</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X46" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
@@ -7256,30 +6903,22 @@
           <t>002.981.424</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>79,35</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>79,35</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>79,35</t>
-        </is>
+      <c r="T47" s="2" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>-79.34999999999999</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>-79.34999999999999</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>ADMINISTRATIVO/COMERCIAL</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X47" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
@@ -7402,30 +7041,22 @@
           <t>1466533</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1.095,27</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1.095,27</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>1.095,27</t>
-        </is>
+      <c r="T48" s="2" t="n">
+        <v>1095.27</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>-1095.27</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>-1095.27</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X48" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
@@ -7548,30 +7179,22 @@
           <t>1189674</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>1.095,27</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1.095,27</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1.095,27</t>
-        </is>
+      <c r="T49" s="2" t="n">
+        <v>1095.27</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>-1095.27</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>-1095.27</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>20/03/2026</t>
-        </is>
+      <c r="X49" s="3" t="n">
+        <v>46101</v>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
@@ -7694,30 +7317,22 @@
           <t>10740</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>62,14</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>62,14</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>62,14</t>
-        </is>
+      <c r="T50" s="2" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>-62.14</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>-62.14</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X50" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
@@ -7840,30 +7455,22 @@
           <t>11785</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>172,72</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>172,72</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>172,72</t>
-        </is>
+      <c r="T51" s="2" t="n">
+        <v>172.72</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>-172.72</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>-172.72</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X51" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
@@ -7986,30 +7593,22 @@
           <t>10829</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>119,68</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>119,68</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>119,68</t>
-        </is>
+      <c r="T52" s="2" t="n">
+        <v>119.68</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>-119.68</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>-119.68</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X52" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
@@ -8132,30 +7731,22 @@
           <t>11882</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>179,64</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>179,64</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>179,64</t>
-        </is>
+      <c r="T53" s="2" t="n">
+        <v>179.64</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>-179.64</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>-179.64</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X53" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
@@ -8278,30 +7869,22 @@
           <t>11965</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>129,25</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>129,25</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>129,25</t>
-        </is>
+      <c r="T54" s="2" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>-129.25</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>-129.25</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X54" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
@@ -8424,30 +8007,22 @@
           <t>11088</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>104,93</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>104,93</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>104,93</t>
-        </is>
+      <c r="T55" s="2" t="n">
+        <v>104.93</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>-104.93</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>-104.93</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X55" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
@@ -8570,30 +8145,22 @@
           <t>11631</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>116,14</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>116,14</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>116,14</t>
-        </is>
+      <c r="T56" s="2" t="n">
+        <v>116.14</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>-116.14</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>-116.14</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X56" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
@@ -8716,30 +8283,22 @@
           <t>10631</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>155,95</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>155,95</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>155,95</t>
-        </is>
+      <c r="T57" s="2" t="n">
+        <v>155.95</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>-155.95</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>-155.95</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X57" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
@@ -8862,30 +8421,22 @@
           <t>12158</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>78,61</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>78,61</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>78,61</t>
-        </is>
+      <c r="T58" s="2" t="n">
+        <v>78.61</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>-78.61</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>-78.61</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X58" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
@@ -9008,30 +8559,22 @@
           <t>11172</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>214,25</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>214,25</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>214,25</t>
-        </is>
+      <c r="T59" s="2" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>-214.25</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>-214.25</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X59" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
@@ -9154,30 +8697,22 @@
           <t>12230</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>89,55</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>89,55</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>89,55</t>
-        </is>
+      <c r="T60" s="2" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>-89.55</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>-89.55</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X60" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
@@ -9300,30 +8835,22 @@
           <t>11266</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>287,46</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>287,46</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>287,46</t>
-        </is>
+      <c r="T61" s="2" t="n">
+        <v>287.46</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>-287.46</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>-287.46</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X61" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
@@ -9446,30 +8973,22 @@
           <t>12698</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>152,39</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>152,39</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>152,39</t>
-        </is>
+      <c r="T62" s="2" t="n">
+        <v>152.39</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>-152.39</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>-152.39</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X62" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
@@ -9592,30 +9111,22 @@
           <t>12346</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>508,09</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>508,09</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>508,09</t>
-        </is>
+      <c r="T63" s="2" t="n">
+        <v>508.09</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>-508.09</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>-508.09</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X63" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
@@ -9738,30 +9249,22 @@
           <t>11699</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>205,61</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>205,61</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>205,61</t>
-        </is>
+      <c r="T64" s="2" t="n">
+        <v>205.61</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>-205.61</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>-205.61</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X64" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
@@ -9884,30 +9387,22 @@
           <t>11366</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>79,64</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>79,64</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>79,64</t>
-        </is>
+      <c r="T65" s="2" t="n">
+        <v>79.64</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>-79.64</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>-79.64</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X65" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
@@ -10030,30 +9525,22 @@
           <t>12412</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>162,65</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>162,65</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>162,65</t>
-        </is>
+      <c r="T66" s="2" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>-162.65</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>-162.65</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X66" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
@@ -10176,30 +9663,22 @@
           <t>11443</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>105,79</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>105,79</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>105,79</t>
-        </is>
+      <c r="T67" s="2" t="n">
+        <v>105.79</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>-105.79</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>-105.79</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X67" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
@@ -10322,30 +9801,22 @@
           <t>12498</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>296,48</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>296,48</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>296,48</t>
-        </is>
+      <c r="T68" s="2" t="n">
+        <v>296.48</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>-296.48</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>-296.48</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X68" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
@@ -10468,30 +9939,22 @@
           <t>10899</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>81,20</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>81,20</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>81,20</t>
-        </is>
+      <c r="T69" s="2" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>-81.2</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>-81.2</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
           <t>FROTA TERCEIRO PRUDENTE</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
+      <c r="X69" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
